--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z989"/>
+  <dimension ref="A1:Z991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>43363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43558</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43661</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>43703</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>43747</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>43754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43776</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43858</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43860</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43943</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43957</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44014</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44127</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44474</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44484</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44503</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44533</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44608</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44624</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44637</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44735</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44792</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44798</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44854</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44865</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44911</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44931</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44956</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44957</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44971</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44986</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45156</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45166</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45212</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45219</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45323</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>43324</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>43334</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>43347</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>43347</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>43347</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>43357</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>43368</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>43370</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>43371</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>43374</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>43388</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>43388</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>43395</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>43397</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>43404</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>43410</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>43412</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>43423</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>43424</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>43426</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>43431</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>43433</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>43437</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>43444</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>43446</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>43455</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>43472</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>43476</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>43490</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>43494</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>43495</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>43497</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43503</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>43514</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43530</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43530</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43539</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43539</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43544</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43551</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43558</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43558</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>43559</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>43560</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>43560</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>43565</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>43567</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>43570</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>43584</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>43616</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>43621</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>43630</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>43635</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>43636</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>43643</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>43643</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>43655</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>43659</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>43661</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>43661</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>43661</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>43668</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>43669</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>43669</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>43669</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>43675</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>43676</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43676</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>43678</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>43679</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>43679</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>43679</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>43682</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>43684</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>43688</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>43688</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>43691</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>43691</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>43697</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>43717</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>43721</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>43725</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>43726</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>43730</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>43738</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>43739</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>43740</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>43745</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>43746</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>43747</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>43752</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>43752</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>43753</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>43756</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>43758</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>43758</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>43774</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>43776</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>43776</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>43776</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>43787</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>43794</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>43795</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>43798</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>43803</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43811</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43811</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>43811</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43823</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43832</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43834</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43834</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43839</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>43846</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>43847</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>43847</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>43853</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>43857</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>43864</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>43872</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>43873</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>43881</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>43885</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>43885</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>43888</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>43889</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>43889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>43893</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>43894</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>43901</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>43901</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>43901</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>43902</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>43902</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>43907</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>43907</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>43911</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>43917</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>43920</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>43922</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>43943</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>43948</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>43955</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>43955</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>43957</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>43958</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>43959</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>43959</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>43959</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>43979</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>43980</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>43983</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>43983</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>43999</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44005</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44007</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44011</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44011</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>44012</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44015</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>44018</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44018</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>44021</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>44023</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44026</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44027</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>44028</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44029</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44039</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>44039</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>44040</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44042</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44043</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44043</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44047</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44049</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44049</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>44053</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44053</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>44054</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>44054</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>44056</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44057</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>44061</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>44062</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>44067</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>44085</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>44085</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>44085</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>44097</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>44098</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>44098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>44104</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>44106</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44109</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>44109</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44110</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44113</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44123</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44127</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>44127</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>44138</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44138</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>44139</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>44140</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44145</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44146</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44152</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44158</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>44158</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>44160</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>44172</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>44178</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>44187</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>44188</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>44193</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44201</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44203</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44208</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44208</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>44208</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44214</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>44218</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44230</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>44237</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>44242</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44242</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>44242</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>44246</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>44246</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>44246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>44248</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>44250</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44250</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44252</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>44252</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>44260</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>44260</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>44260</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>44263</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>44263</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>44265</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44270</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44281</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44281</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44285</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44292</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44292</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44293</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44296</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44297</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44297</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44301</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>44301</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>44302</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44302</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>44302</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>44307</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>44309</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44323</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44328</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44344</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44350</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>44350</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>44358</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>44360</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>44360</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44360</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44365</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>44365</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>44365</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>44371</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>44378</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44379</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44381</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>44381</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>44384</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>44384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>44384</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>44386</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>44391</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>44398</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>44404</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>44411</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44414</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44423</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44423</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44425</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44425</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>44425</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>44431</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>44432</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>44433</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>44435</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>44439</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>44440</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>44448</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>44448</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>44448</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>44449</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>44449</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>44449</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>44450</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44452</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>44453</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>44453</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>44454</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>44454</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>44458</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>44458</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>44463</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>44463</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>44466</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44470</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44472</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>44473</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>44473</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>44484</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44487</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44490</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44495</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44495</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44495</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44501</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44508</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44508</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>44511</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44517</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44518</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>44518</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44522</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44522</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44524</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44531</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44535</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44536</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>44553</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44566</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44571</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>44572</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44579</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44580</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
         <v>44580</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>44588</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44594</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44596</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44596</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44604</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44608</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>44610</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44610</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44614</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44616</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44624</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44624</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44636</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44636</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44636</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44637</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44637</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44640</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44643</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44643</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44643</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44648</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44667</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44671</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44671</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>44676</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44680</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44697</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>44697</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>44701</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>44704</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>44705</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>44715</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>44715</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>44719</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44720</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44722</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>44722</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44724</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>44725</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>44733</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44741</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>44742</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44745</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44745</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>44746</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>44752</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44752</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44752</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>44753</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44761</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44769</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44769</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>44770</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>44771</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>44774</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>44778</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>44778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44782</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44785</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>44785</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>44785</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44791</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44795</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>44796</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>44803</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44807</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>44807</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44814</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>44817</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>44818</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>44818</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>44818</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>44819</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>44823</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>44824</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44826</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44830</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>44834</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>44837</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>44838</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44838</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44838</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>44841</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>44846</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>44846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>44848</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>44848</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>44848</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>44852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>44854</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>44854</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>44854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>44855</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>44859</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>44859</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44864</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>44868</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44868</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44869</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>44872</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44887</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>44887</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>44887</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>44895</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>44895</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>44895</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>44897</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44897</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44899</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44899</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>44900</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>44900</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>44902</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>44907</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>44907</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>44907</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44908</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44909</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44909</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>44909</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>44911</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>44911</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>44914</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>44917</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>44931</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>44942</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>44949</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>44953</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>44957</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>44957</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>44957</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>44958</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42220,7 +42220,7 @@
         <v>44958</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>44958</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>44960</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>44966</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>44970</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>44972</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>44974</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>44977</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>44979</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>44979</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>44979</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>44980</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44985</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44985</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44986</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44988</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44991</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44991</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44998</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>45001</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>45001</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45007</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45007</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45008</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45012</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45013</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45014</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>45014</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45014</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45016</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45022</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45022</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45022</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45029</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45030</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45030</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45034</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45036</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45036</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45039</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45039</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45039</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45041</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45043</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45048</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45053</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45056</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45056</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>45056</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>45057</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45065</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45066</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45068</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45070</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45070</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45073</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46414,7 +46414,7 @@
         <v>45073</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         <v>45079</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>45081</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45081</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46642,7 +46642,7 @@
         <v>45082</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>45091</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45097</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45098</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45098</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45099</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45103</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45103</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45104</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45104</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45105</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45105</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45110</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45110</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45112</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45113</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45114</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45114</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45114</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45118</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45119</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45121</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45121</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45121</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45140</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45140</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45140</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45141</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>45141</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45142</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45147</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45148</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49111,7 +49111,7 @@
         <v>45149</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45154</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45155</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45156</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45156</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45159</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45159</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>45160</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49587,7 +49587,7 @@
         <v>45160</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45160</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49711,7 +49711,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>45161</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>45161</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45162</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45163</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>45163</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         <v>45163</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45166</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50400,7 +50400,7 @@
         <v>45166</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50514,7 +50514,7 @@
         <v>45168</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>45169</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>45169</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>45169</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45170</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50804,7 +50804,7 @@
         <v>45174</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>45175</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>45175</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>45176</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
         <v>45180</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>45182</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45182</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45182</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45183</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>45183</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51741,7 +51741,7 @@
         <v>45189</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51798,7 +51798,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51860,7 +51860,7 @@
         <v>45191</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51917,7 +51917,7 @@
         <v>45191</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>45191</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52031,7 +52031,7 @@
         <v>45192</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>45193</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>45193</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45195</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45195</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52321,7 +52321,7 @@
         <v>45195</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52378,7 +52378,7 @@
         <v>45196</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52440,7 +52440,7 @@
         <v>45196</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>45196</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52559,7 +52559,7 @@
         <v>45201</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>45202</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45205</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45205</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>45205</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52926,7 +52926,7 @@
         <v>45209</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45212</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>45212</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53801,7 +53801,7 @@
         <v>45213</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53863,7 +53863,7 @@
         <v>45213</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53925,7 +53925,7 @@
         <v>45214</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53982,7 +53982,7 @@
         <v>45214</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54039,7 +54039,7 @@
         <v>45215</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54096,7 +54096,7 @@
         <v>45215</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54153,7 +54153,7 @@
         <v>45216</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54277,7 +54277,7 @@
         <v>45218</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54334,7 +54334,7 @@
         <v>45218</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54562,7 +54562,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54619,7 +54619,7 @@
         <v>45224</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45225</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>45225</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54795,7 +54795,7 @@
         <v>45225</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54909,7 +54909,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54966,7 +54966,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55023,7 +55023,7 @@
         <v>45226</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55080,7 +55080,7 @@
         <v>45228</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55137,7 +55137,7 @@
         <v>45228</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55194,7 +55194,7 @@
         <v>45230</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55251,7 +55251,7 @@
         <v>45230</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55308,7 +55308,7 @@
         <v>45230</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55365,7 +55365,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55422,7 +55422,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55479,7 +55479,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>45231</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55650,7 +55650,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45231</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45237</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56074,7 +56074,7 @@
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>45240</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>45243</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>45243</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56540,7 +56540,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45250</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>45250</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>45250</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56959,7 +56959,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57078,7 +57078,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45251</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         <v>45252</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57306,7 +57306,7 @@
         <v>45253</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57363,7 +57363,7 @@
         <v>45256</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57420,7 +57420,7 @@
         <v>45256</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57477,7 +57477,7 @@
         <v>45256</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57534,7 +57534,7 @@
         <v>45257</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         <v>45260</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57648,7 +57648,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45264</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45264</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45266</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45268</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45268</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45270</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45271</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58161,7 +58161,7 @@
         <v>45272</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45272</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45278</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45280</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45299</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45299</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45302</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58679,7 +58679,7 @@
         <v>45303</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>45303</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>45306</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58860,7 +58860,7 @@
         <v>45309</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58917,7 +58917,7 @@
         <v>45311</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58974,7 +58974,7 @@
         <v>45311</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59031,7 +59031,7 @@
         <v>45311</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45313</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>45314</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59195,14 +59195,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 2968-2024</t>
+          <t>A 2930-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59214,13 +59214,8 @@
           <t>FLEN</t>
         </is>
       </c>
-      <c r="F969" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G969" t="n">
-        <v>10.3</v>
+        <v>2.2</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -59257,14 +59252,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 2930-2024</t>
+          <t>A 2901-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59277,7 +59272,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59314,14 +59309,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 2901-2024</t>
+          <t>A 2968-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59333,8 +59328,13 @@
           <t>FLEN</t>
         </is>
       </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G971" t="n">
-        <v>2.6</v>
+        <v>10.3</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59378,7 +59378,7 @@
         <v>45320</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45321</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45321</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45321</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>45322</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45322</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45323</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>45323</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59834,7 +59834,7 @@
         <v>45323</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45327</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45327</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45328</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>45328</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>45328</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>45330</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60238,7 +60238,7 @@
         <v>45330</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45331</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60347,62 +60347,176 @@
       </c>
       <c r="R988" s="2" t="inlineStr"/>
     </row>
-    <row r="989">
+    <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 5960-2024</t>
+          <t>A 6097-2024</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
-        <v>45336</v>
+        <v>45337</v>
       </c>
       <c r="C989" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G989" t="n">
+        <v>28</v>
+      </c>
+      <c r="H989" t="n">
+        <v>0</v>
+      </c>
+      <c r="I989" t="n">
+        <v>0</v>
+      </c>
+      <c r="J989" t="n">
+        <v>0</v>
+      </c>
+      <c r="K989" t="n">
+        <v>0</v>
+      </c>
+      <c r="L989" t="n">
+        <v>0</v>
+      </c>
+      <c r="M989" t="n">
+        <v>0</v>
+      </c>
+      <c r="N989" t="n">
+        <v>0</v>
+      </c>
+      <c r="O989" t="n">
+        <v>0</v>
+      </c>
+      <c r="P989" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q989" t="n">
+        <v>0</v>
+      </c>
+      <c r="R989" s="2" t="inlineStr"/>
+    </row>
+    <row r="990" ht="15" customHeight="1">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>A 6109-2024</t>
+        </is>
+      </c>
+      <c r="B990" s="1" t="n">
         <v>45337</v>
       </c>
-      <c r="D989" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E989" t="inlineStr">
-        <is>
-          <t>FLEN</t>
-        </is>
-      </c>
-      <c r="G989" t="n">
+      <c r="C990" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G990" t="n">
+        <v>4</v>
+      </c>
+      <c r="H990" t="n">
+        <v>0</v>
+      </c>
+      <c r="I990" t="n">
+        <v>0</v>
+      </c>
+      <c r="J990" t="n">
+        <v>0</v>
+      </c>
+      <c r="K990" t="n">
+        <v>0</v>
+      </c>
+      <c r="L990" t="n">
+        <v>0</v>
+      </c>
+      <c r="M990" t="n">
+        <v>0</v>
+      </c>
+      <c r="N990" t="n">
+        <v>0</v>
+      </c>
+      <c r="O990" t="n">
+        <v>0</v>
+      </c>
+      <c r="P990" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q990" t="n">
+        <v>0</v>
+      </c>
+      <c r="R990" s="2" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>A 6104-2024</t>
+        </is>
+      </c>
+      <c r="B991" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C991" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G991" t="n">
         <v>4.8</v>
       </c>
-      <c r="H989" t="n">
-        <v>0</v>
-      </c>
-      <c r="I989" t="n">
-        <v>0</v>
-      </c>
-      <c r="J989" t="n">
-        <v>0</v>
-      </c>
-      <c r="K989" t="n">
-        <v>0</v>
-      </c>
-      <c r="L989" t="n">
-        <v>0</v>
-      </c>
-      <c r="M989" t="n">
-        <v>0</v>
-      </c>
-      <c r="N989" t="n">
-        <v>0</v>
-      </c>
-      <c r="O989" t="n">
-        <v>0</v>
-      </c>
-      <c r="P989" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q989" t="n">
-        <v>0</v>
-      </c>
-      <c r="R989" s="2" t="inlineStr"/>
+      <c r="H991" t="n">
+        <v>0</v>
+      </c>
+      <c r="I991" t="n">
+        <v>0</v>
+      </c>
+      <c r="J991" t="n">
+        <v>0</v>
+      </c>
+      <c r="K991" t="n">
+        <v>0</v>
+      </c>
+      <c r="L991" t="n">
+        <v>0</v>
+      </c>
+      <c r="M991" t="n">
+        <v>0</v>
+      </c>
+      <c r="N991" t="n">
+        <v>0</v>
+      </c>
+      <c r="O991" t="n">
+        <v>0</v>
+      </c>
+      <c r="P991" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q991" t="n">
+        <v>0</v>
+      </c>
+      <c r="R991" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z991"/>
+  <dimension ref="A1:Z992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>43363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43558</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43661</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>43703</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>43747</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>43754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43776</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43858</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43860</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43943</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43957</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44014</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44127</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44474</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44484</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44503</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44533</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44608</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44624</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44637</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44735</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44792</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44798</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44854</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44865</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44911</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44931</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44956</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44957</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44971</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44986</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45156</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45166</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45212</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45219</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45323</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45337</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43324</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43334</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43347</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43347</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43357</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43368</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>43370</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43374</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43388</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43388</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43395</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43397</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43404</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43410</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43412</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43423</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>43424</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43433</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43437</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43455</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43472</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43476</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43494</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43497</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43503</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43514</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43522</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43530</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43530</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43535</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43538</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43539</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43539</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43544</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43558</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>43558</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43560</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43560</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43565</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43570</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>43584</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>43616</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>43621</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>43630</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>43636</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>43643</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>43643</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>43655</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43659</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43661</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43661</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43661</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>43668</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43669</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43669</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43669</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43675</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43676</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43676</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43678</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43679</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>43679</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>43684</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>43688</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>43688</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>43691</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>43717</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>43721</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>43725</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>43726</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43730</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43738</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>43739</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>43740</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>43745</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>43746</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>43747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43752</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43752</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>43753</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>43756</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43758</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43758</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>43762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43769</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43776</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43776</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>43776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43787</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43794</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>43795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>43798</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43803</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>43811</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>43811</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>43811</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>43823</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>43832</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>43834</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>43834</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>43839</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>43846</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>43847</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>43847</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>43853</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>43857</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>43864</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>43872</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>43873</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>43881</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>43885</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>43885</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>43888</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>43889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>43889</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>43893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>43894</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>43901</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>43901</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>43901</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>43902</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43902</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43907</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43907</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43911</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43917</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43920</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43922</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43943</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43948</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43955</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43955</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43957</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43958</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43959</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43959</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43959</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43980</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>43983</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>43983</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>43983</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>43985</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>43998</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>43999</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44007</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44011</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44011</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44015</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44018</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44021</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44023</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44026</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44029</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44039</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44039</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44040</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44042</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44043</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44043</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44047</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44049</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44049</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44053</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44053</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44054</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44054</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44056</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44057</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44061</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44085</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44085</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44085</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44089</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44097</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44098</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44104</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44106</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44109</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44109</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44113</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44123</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44127</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44127</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44138</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44138</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44139</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44140</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44145</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44146</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44152</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44158</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44158</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44160</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44172</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44178</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44187</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44188</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44193</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44201</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44203</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44208</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44208</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44208</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44218</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44230</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44237</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44242</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44242</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44242</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44246</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44246</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44248</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44250</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44250</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44252</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44252</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44260</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44260</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44260</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44263</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44263</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44265</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44270</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44281</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44285</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44292</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44292</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44293</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44297</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44297</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44301</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44301</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>44302</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44302</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44302</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44307</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44309</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44323</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44323</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44328</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44350</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44350</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44358</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44360</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44360</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44360</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44365</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44365</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44365</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44371</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44379</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44381</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44381</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44384</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44386</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>44391</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44411</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44413</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44414</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44414</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>44421</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44423</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44423</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44425</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44425</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44431</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44433</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44435</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44448</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44448</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44448</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44449</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44449</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44449</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44450</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44452</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44453</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44453</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44454</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44458</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44458</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44463</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44466</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44472</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>44473</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44484</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44487</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44495</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44495</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44508</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44508</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44511</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44518</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44522</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>44522</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44524</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44531</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44535</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44536</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44553</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44566</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44571</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44572</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44579</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44580</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44580</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44596</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44596</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44604</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44608</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44610</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44610</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44616</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44624</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44624</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44636</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44636</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44636</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44637</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44637</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44640</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44643</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44643</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44643</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44671</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44671</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44676</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44680</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44697</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44697</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44701</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44715</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44715</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44720</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44722</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44722</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44724</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44725</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44733</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44742</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44745</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44745</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44746</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44752</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44752</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44752</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44753</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>44761</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44769</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44769</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44770</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44771</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44774</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44782</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44785</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44785</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44785</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44791</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44795</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44796</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44803</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44807</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44807</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44814</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44817</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44818</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44818</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44818</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44823</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>44826</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44830</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44834</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>44837</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44838</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44838</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44838</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44848</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44848</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44848</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44854</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44854</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44859</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44859</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>44864</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44868</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44872</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44873</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44881</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44887</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44887</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44887</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44895</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44895</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>44897</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44897</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44899</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44899</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44900</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44900</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44902</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44907</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>44907</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44907</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44908</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44909</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44909</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44909</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44911</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44911</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44914</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>44917</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>44931</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>44942</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44943</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>44953</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44957</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44957</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44958</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44958</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44960</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44966</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44977</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44977</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44979</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44979</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44980</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44985</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44985</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44986</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>44988</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44991</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44991</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44998</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45001</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45001</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45007</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45007</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45012</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45013</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45014</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45014</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45014</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>45016</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45022</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45022</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45022</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45029</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45030</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45030</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45034</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45036</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45036</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45039</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45039</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45039</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45041</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45043</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45048</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45053</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45056</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45056</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45056</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45057</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45065</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45066</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45068</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45070</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45073</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45073</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45079</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45081</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45081</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45082</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45091</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45098</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45098</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45103</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45103</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45104</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45104</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45105</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45105</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45110</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45110</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45112</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45113</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45114</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45114</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45114</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45118</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45119</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45121</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45121</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45121</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45140</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45140</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45140</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45141</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45141</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45142</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45147</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45148</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45154</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45155</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45156</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45156</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45159</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45159</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45160</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45160</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45160</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45161</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45161</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45161</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45162</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45163</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45163</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45163</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45166</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45166</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45168</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45169</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45169</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45169</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45170</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45174</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45175</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45175</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45176</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45180</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45182</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45182</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45182</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45183</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45183</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45187</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45189</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45189</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45191</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45191</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45191</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45192</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45193</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45193</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45195</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45195</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45195</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45196</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45196</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45196</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45205</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45205</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45205</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45209</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45211</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45212</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45212</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45213</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45213</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45214</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45214</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45215</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45215</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45216</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45218</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45222</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45224</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45225</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45225</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45225</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45226</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45228</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45228</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45230</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>45230</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45230</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45231</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45231</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45243</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45243</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45250</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45250</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45251</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45252</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45253</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45256</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>45256</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45256</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45257</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45264</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45264</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45266</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45268</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45268</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45270</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45271</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45272</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45272</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45278</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45280</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45299</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45299</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45299</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45302</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45303</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45303</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45306</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45309</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45311</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59052,14 +59052,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 2448-2024</t>
+          <t>A 2449-2024</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45311</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -59109,14 +59109,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 2449-2024</t>
+          <t>A 2448-2024</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45311</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59129,7 +59129,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -59173,7 +59173,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45314</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59280,14 +59280,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 2901-2024</t>
+          <t>A 2930-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59300,7 +59300,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59337,14 +59337,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 2968-2024</t>
+          <t>A 2901-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59356,13 +59356,8 @@
           <t>FLEN</t>
         </is>
       </c>
-      <c r="F971" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G971" t="n">
-        <v>10.3</v>
+        <v>2.6</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59399,14 +59394,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 2930-2024</t>
+          <t>A 2968-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59418,8 +59413,13 @@
           <t>FLEN</t>
         </is>
       </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G972" t="n">
-        <v>2.2</v>
+        <v>10.3</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -59463,7 +59463,7 @@
         <v>45320</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59513,14 +59513,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 3774-2024</t>
+          <t>A 3648-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59570,14 +59570,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 3648-2024</t>
+          <t>A 3774-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59634,7 +59634,7 @@
         <v>45321</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59684,14 +59684,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 3909-2024</t>
+          <t>A 3926-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59741,14 +59741,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 3926-2024</t>
+          <t>A 3909-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59805,7 +59805,7 @@
         <v>45323</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45323</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45323</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45327</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45327</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60083,14 +60083,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 4778-2024</t>
+          <t>A 4724-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -60140,14 +60140,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 4657-2024</t>
+          <t>A 4778-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60160,7 +60160,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -60197,14 +60197,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 4724-2024</t>
+          <t>A 4657-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -60261,7 +60261,7 @@
         <v>45330</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45330</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45331</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60442,7 +60442,7 @@
         <v>45337</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
       </c>
       <c r="R990" s="2" t="inlineStr"/>
     </row>
-    <row r="991">
+    <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
           <t>A 6109-2024</t>
@@ -60499,7 +60499,7 @@
         <v>45337</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60545,6 +60545,63 @@
         <v>0</v>
       </c>
       <c r="R991" s="2" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>A 6530-2024</t>
+        </is>
+      </c>
+      <c r="B992" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C992" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G992" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H992" t="n">
+        <v>0</v>
+      </c>
+      <c r="I992" t="n">
+        <v>0</v>
+      </c>
+      <c r="J992" t="n">
+        <v>0</v>
+      </c>
+      <c r="K992" t="n">
+        <v>0</v>
+      </c>
+      <c r="L992" t="n">
+        <v>0</v>
+      </c>
+      <c r="M992" t="n">
+        <v>0</v>
+      </c>
+      <c r="N992" t="n">
+        <v>0</v>
+      </c>
+      <c r="O992" t="n">
+        <v>0</v>
+      </c>
+      <c r="P992" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q992" t="n">
+        <v>0</v>
+      </c>
+      <c r="R992" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z992"/>
+  <dimension ref="A1:Z994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>43363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43558</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43661</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>43703</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>43747</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>43754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43776</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43858</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43860</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43943</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43957</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44014</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44127</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44474</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44484</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44503</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44533</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44608</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44624</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44637</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44735</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44792</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44798</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44854</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44865</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44911</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44931</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44956</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44957</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44971</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44986</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45156</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45166</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45212</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45219</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45323</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45337</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43324</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43334</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43347</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43347</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43357</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43368</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>43370</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43374</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43388</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43388</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43395</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43397</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43404</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43410</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43412</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43423</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>43424</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43433</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43437</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43455</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43472</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43476</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43494</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43497</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43503</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43514</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43522</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43530</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43530</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43535</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43538</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43539</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43539</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43544</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43558</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>43558</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43560</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43560</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43565</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43570</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>43584</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>43616</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>43621</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>43630</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>43636</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>43643</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>43643</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>43655</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43659</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43661</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43661</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43661</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>43668</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43669</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43669</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43669</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43675</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43676</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43676</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43678</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43679</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>43679</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>43684</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>43688</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>43688</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>43691</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>43717</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>43721</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>43725</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>43726</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43730</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43738</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>43739</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>43740</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>43745</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>43746</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>43747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43752</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43752</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>43753</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>43756</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43758</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43758</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>43762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43769</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43776</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43776</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>43776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43787</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43794</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>43795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>43798</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43803</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>43811</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>43811</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>43811</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>43823</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>43832</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>43834</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>43834</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>43839</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>43846</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>43847</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>43847</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>43853</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>43857</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>43864</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>43872</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>43873</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>43881</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>43885</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>43885</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>43888</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>43889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>43889</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>43893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>43894</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>43901</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>43901</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>43901</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>43902</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43902</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43907</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43907</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43911</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43917</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43920</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43922</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43943</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43948</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43955</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43955</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43957</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43958</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43959</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43959</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43959</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43980</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>43983</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>43983</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>43983</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>43985</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>43998</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>43999</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44007</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44011</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44011</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44015</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44018</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44021</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44023</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44026</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44029</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44039</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44039</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44040</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44042</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44043</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44043</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44047</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44049</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44049</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44053</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44053</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44054</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44054</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44056</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44057</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44061</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44085</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44085</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44085</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44089</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44097</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44098</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44104</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44106</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44109</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44109</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44113</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44123</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44127</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44127</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44138</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44138</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44139</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44140</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44145</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44146</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44152</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44158</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44158</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44160</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44172</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44178</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44187</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44188</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44193</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44201</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44203</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44208</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44208</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44208</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44218</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44230</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44237</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44242</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44242</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44242</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44246</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44246</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44248</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44250</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44250</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44252</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44252</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44260</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44260</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44260</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44263</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44263</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44265</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44270</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44281</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44285</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44292</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44292</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44293</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44297</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44297</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44301</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44301</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>44302</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44302</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44302</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44307</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44309</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44323</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44323</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44328</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44350</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44350</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44358</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44360</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44360</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44360</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44365</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44365</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44365</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44371</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44379</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44381</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44381</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44384</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44386</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>44391</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44411</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44413</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44414</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44414</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>44421</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44423</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44423</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44425</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44425</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44431</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44433</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44435</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44448</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44448</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44448</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44449</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44449</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44449</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44450</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44452</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44453</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44453</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44454</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44458</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44458</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44463</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44466</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44472</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>44473</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44484</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44487</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44495</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44495</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44508</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44508</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44511</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44518</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44522</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>44522</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44524</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44531</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44535</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44536</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44553</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44566</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44571</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44572</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44579</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44580</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44580</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44596</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44596</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44604</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44608</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44610</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44610</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44616</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44624</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44624</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44636</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44636</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44636</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44637</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44637</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44640</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44643</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44643</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44643</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44671</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44671</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44676</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44680</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44697</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44697</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44701</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44715</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44715</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44720</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44722</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44722</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44724</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44725</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44733</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44742</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44745</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44745</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44746</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44752</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44752</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44752</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44753</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>44761</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44769</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44769</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44770</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44771</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44774</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44782</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44785</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44785</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44785</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44791</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44795</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44796</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44803</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44807</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44807</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44814</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44817</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44818</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44818</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44818</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44823</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>44826</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44830</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44834</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>44837</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44838</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44838</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44838</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44848</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44848</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44848</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44854</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44854</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44859</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44859</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>44864</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44868</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44872</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44873</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44881</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44887</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44887</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44887</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44895</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44895</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>44897</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44897</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44899</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44899</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44900</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44900</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44902</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44907</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>44907</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44907</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44908</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44909</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44909</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44909</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44911</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44911</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44914</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>44917</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>44931</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>44942</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44943</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>44953</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44957</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44957</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44958</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44958</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44960</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44966</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44977</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44977</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44979</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44979</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44980</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44985</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44985</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44986</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>44988</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44991</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44991</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44998</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45001</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45001</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45007</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45007</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45012</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45013</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45014</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45014</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45014</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>45016</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45022</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45022</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45022</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45029</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45030</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45030</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45034</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45036</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45036</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45039</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45039</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45039</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45041</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45043</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45048</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45053</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45056</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45056</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45056</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45057</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45065</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45066</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45068</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45070</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45073</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45073</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45079</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45081</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45081</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45082</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45091</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45098</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45098</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45103</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45103</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45104</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45104</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45105</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45105</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45110</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45110</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45112</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45113</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45114</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45114</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45114</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45118</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45119</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45121</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45121</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45121</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45140</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45140</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45140</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45141</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45141</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45142</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45147</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45148</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45154</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45155</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45156</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45156</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45159</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45159</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45160</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45160</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45160</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45161</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45161</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45161</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45162</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45163</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45163</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45163</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45166</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45166</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45168</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45169</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45169</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45169</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45170</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45174</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45175</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45175</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45176</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45180</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45182</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45182</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45182</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45183</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45183</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45187</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45189</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45189</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45191</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45191</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45191</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45192</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45193</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45193</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45195</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45195</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45195</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45196</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45196</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45196</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45205</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45205</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45205</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45209</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45211</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45212</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45212</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45213</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45213</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45214</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45214</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45215</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45215</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45216</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45218</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45222</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45224</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45225</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45225</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45225</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45226</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45228</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45228</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45230</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>45230</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45230</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45231</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45231</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45243</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45243</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45250</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45250</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45251</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45252</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45253</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45256</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>45256</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45256</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45257</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45264</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45264</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45266</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45268</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45268</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45270</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45271</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45272</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45272</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45278</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45280</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45299</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45299</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45299</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45302</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45303</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45303</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45306</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45309</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45311</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45311</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45311</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45314</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45315</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59344,7 +59344,7 @@
         <v>45315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59401,7 +59401,7 @@
         <v>45315</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45320</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45321</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45321</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45321</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45322</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45322</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45323</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45323</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45323</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45327</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45327</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60083,14 +60083,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 4724-2024</t>
+          <t>A 4657-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -60140,14 +60140,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 4778-2024</t>
+          <t>A 4724-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60160,7 +60160,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -60197,14 +60197,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 4657-2024</t>
+          <t>A 4778-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -60261,7 +60261,7 @@
         <v>45330</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45330</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45331</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60442,7 +60442,7 @@
         <v>45337</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45337</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
       </c>
       <c r="R991" s="2" t="inlineStr"/>
     </row>
-    <row r="992">
+    <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
           <t>A 6530-2024</t>
@@ -60556,7 +60556,7 @@
         <v>45341</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60602,6 +60602,120 @@
         <v>0</v>
       </c>
       <c r="R992" s="2" t="inlineStr"/>
+    </row>
+    <row r="993" ht="15" customHeight="1">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>A 6964-2024</t>
+        </is>
+      </c>
+      <c r="B993" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C993" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G993" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H993" t="n">
+        <v>0</v>
+      </c>
+      <c r="I993" t="n">
+        <v>0</v>
+      </c>
+      <c r="J993" t="n">
+        <v>0</v>
+      </c>
+      <c r="K993" t="n">
+        <v>0</v>
+      </c>
+      <c r="L993" t="n">
+        <v>0</v>
+      </c>
+      <c r="M993" t="n">
+        <v>0</v>
+      </c>
+      <c r="N993" t="n">
+        <v>0</v>
+      </c>
+      <c r="O993" t="n">
+        <v>0</v>
+      </c>
+      <c r="P993" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q993" t="n">
+        <v>0</v>
+      </c>
+      <c r="R993" s="2" t="inlineStr"/>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>A 6982-2024</t>
+        </is>
+      </c>
+      <c r="B994" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C994" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G994" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H994" t="n">
+        <v>0</v>
+      </c>
+      <c r="I994" t="n">
+        <v>0</v>
+      </c>
+      <c r="J994" t="n">
+        <v>0</v>
+      </c>
+      <c r="K994" t="n">
+        <v>0</v>
+      </c>
+      <c r="L994" t="n">
+        <v>0</v>
+      </c>
+      <c r="M994" t="n">
+        <v>0</v>
+      </c>
+      <c r="N994" t="n">
+        <v>0</v>
+      </c>
+      <c r="O994" t="n">
+        <v>0</v>
+      </c>
+      <c r="P994" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q994" t="n">
+        <v>0</v>
+      </c>
+      <c r="R994" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>43363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43558</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43661</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>43703</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>43747</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>43754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43776</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43858</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43860</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43943</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43957</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44014</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44127</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44474</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44484</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44503</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44533</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44608</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44624</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44637</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44735</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44792</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44798</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44854</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44865</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44911</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44931</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44956</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44957</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44971</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44986</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45156</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45166</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45212</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45219</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45323</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45337</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43324</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43334</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43347</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43347</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43357</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43368</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>43370</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43374</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43388</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43388</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43395</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43397</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43404</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43410</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43412</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43423</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>43424</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43433</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43437</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43455</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43472</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43476</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43494</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43497</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43503</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43514</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43522</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43530</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43530</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43535</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43538</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43539</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43539</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43544</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43558</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>43558</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43560</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43560</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43565</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43570</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>43584</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>43616</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>43621</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>43630</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>43636</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>43643</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>43643</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>43655</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43659</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43661</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43661</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43661</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>43668</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43669</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43669</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43669</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43675</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43676</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43676</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43678</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43679</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>43679</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>43684</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>43688</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>43688</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>43691</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>43717</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>43721</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>43725</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>43726</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43730</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43738</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>43739</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>43740</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>43745</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>43746</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>43747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43752</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43752</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>43753</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>43756</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43758</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43758</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>43762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43769</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43776</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43776</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>43776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43787</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43794</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>43795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>43798</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43803</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>43811</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>43811</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>43811</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>43823</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>43832</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>43834</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>43834</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>43839</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>43846</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>43847</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>43847</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>43853</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>43857</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>43864</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>43872</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>43873</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>43881</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>43885</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>43885</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>43888</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>43889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>43889</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>43893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>43894</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>43901</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>43901</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>43901</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>43902</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43902</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43907</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43907</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43911</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43917</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43920</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43922</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43943</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43948</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43955</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43955</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43957</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43958</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43959</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43959</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43959</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43980</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>43983</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>43983</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>43983</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>43985</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>43998</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>43999</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44007</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44011</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44011</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44015</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44018</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44021</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44023</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44026</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44029</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44039</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44039</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44040</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44042</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44043</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44043</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44047</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44049</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44049</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44053</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44053</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44054</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44054</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44056</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44057</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44061</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44085</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44085</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44085</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44089</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44097</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44098</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44104</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44106</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44109</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44109</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44113</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44123</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44127</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44127</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44138</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44138</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44139</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44140</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44145</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44146</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44152</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44158</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44158</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44160</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44172</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44178</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44187</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44188</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44193</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44201</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44203</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44208</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44208</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44208</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44218</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44230</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44237</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44242</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44242</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44242</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44246</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44246</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44248</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44250</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44250</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44252</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44252</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44260</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44260</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44260</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44263</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44263</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44265</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44270</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44281</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44285</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44292</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44292</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44293</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44297</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44297</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44301</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44301</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>44302</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44302</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44302</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44307</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44309</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44323</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44323</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44328</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44350</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44350</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44358</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44360</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44360</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44360</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44365</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44365</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44365</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44371</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44379</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44381</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44381</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44384</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44386</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>44391</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44411</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44413</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44414</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44414</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>44421</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44423</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44423</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44425</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44425</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44431</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44433</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44435</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44448</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44448</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44448</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44449</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44449</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44449</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44450</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44452</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44453</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44453</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44454</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44458</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44458</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44463</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44466</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44472</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>44473</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44484</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44487</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44495</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44495</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44508</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44508</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44511</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44518</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44522</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>44522</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44524</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44531</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44535</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44536</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44553</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44566</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44571</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44572</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44579</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44580</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44580</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44596</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44596</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44604</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44608</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44610</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44610</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44616</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44624</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44624</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44636</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44636</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44636</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44637</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44637</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44640</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44643</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44643</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44643</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44671</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44671</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44676</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44680</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44697</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44697</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44701</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44715</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44715</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44720</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44722</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44722</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44724</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44725</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44733</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44742</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44745</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44745</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44746</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44752</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44752</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44752</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44753</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>44761</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44769</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44769</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44770</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44771</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44774</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44782</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44785</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44785</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44785</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44791</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44795</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44796</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44803</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44807</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44807</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44814</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44817</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44818</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44818</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44818</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44823</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>44826</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44830</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44834</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>44837</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44838</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44838</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44838</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44848</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44848</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44848</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44854</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44854</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44859</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44859</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>44864</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44868</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44872</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44873</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44881</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44887</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44887</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44887</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44895</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44895</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>44897</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44897</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44899</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44899</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44900</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44900</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44902</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44907</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>44907</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44907</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44908</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44909</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44909</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44909</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44911</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44911</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44914</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>44917</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>44931</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>44942</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44943</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>44953</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44957</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44957</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44958</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44958</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44960</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44966</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44977</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44977</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44979</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44979</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44980</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44985</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44985</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44986</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>44988</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44991</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44991</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44998</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45001</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45001</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45007</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45007</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45012</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45013</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45014</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45014</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45014</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>45016</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45022</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45022</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45022</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45029</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45030</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45030</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45034</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45036</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45036</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45039</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45039</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45039</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45041</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45043</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45048</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45053</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45056</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45056</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45056</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45057</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45065</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45066</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45068</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45070</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45073</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45073</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45079</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45081</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45081</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45082</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45091</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45098</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45098</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45103</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45103</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45104</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45104</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45105</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45105</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45110</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45110</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45112</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45113</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45114</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45114</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45114</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45118</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45119</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45121</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45121</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45121</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45140</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45140</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45140</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45141</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45141</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45142</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45147</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45148</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45154</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45155</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45156</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45156</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45159</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45159</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45160</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45160</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45160</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45161</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45161</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45161</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45162</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45163</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45163</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45163</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45166</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45166</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45168</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45169</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45169</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45169</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45170</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45174</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45175</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45175</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45176</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45180</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45182</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45182</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45182</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45183</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45183</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45187</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45189</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45189</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45191</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45191</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45191</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45192</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45193</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45193</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45195</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45195</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45195</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45196</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45196</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45196</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45205</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45205</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45205</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45209</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45211</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45212</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45212</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45213</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45213</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45214</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45214</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45215</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45215</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45216</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45218</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45222</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45224</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45225</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45225</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45225</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45226</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45228</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45228</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45230</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>45230</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45230</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45231</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45231</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45243</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45243</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45250</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45250</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45251</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45252</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45253</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45256</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>45256</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45256</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45257</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45264</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45264</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45266</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45268</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45268</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45270</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45271</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45272</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45272</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45278</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45280</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45299</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45299</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45299</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45302</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45303</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45303</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45306</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45309</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45311</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45311</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45311</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45314</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45315</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59344,7 +59344,7 @@
         <v>45315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59401,7 +59401,7 @@
         <v>45315</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45320</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45321</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45321</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45321</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45322</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45322</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45323</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45323</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45323</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45327</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45327</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60083,14 +60083,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 4657-2024</t>
+          <t>A 4724-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -60140,14 +60140,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 4724-2024</t>
+          <t>A 4657-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60160,7 +60160,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -60204,7 +60204,7 @@
         <v>45328</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60261,7 +60261,7 @@
         <v>45330</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45330</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45331</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60435,14 +60435,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 6104-2024</t>
+          <t>A 6109-2024</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -60492,14 +60492,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 6109-2024</t>
+          <t>A 6104-2024</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60512,7 +60512,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -60556,7 +60556,7 @@
         <v>45341</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45343</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45343</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z994"/>
+  <dimension ref="A1:Z998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>43363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43558</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43661</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>43703</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>43747</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>43754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43776</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43858</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43860</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43943</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43957</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44014</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44127</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44474</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44484</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44503</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44533</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44608</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44624</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44637</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44735</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44792</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44798</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44854</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44865</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44911</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44931</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44956</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44957</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44971</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44986</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45156</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45166</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45212</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45219</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45323</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45337</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43324</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43334</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43347</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43347</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43357</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43368</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>43370</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43374</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43388</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43388</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43395</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43397</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43404</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43410</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43412</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43423</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>43424</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43433</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43437</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43455</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43472</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43476</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43494</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43497</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43503</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43514</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43522</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43530</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43530</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43535</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43538</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43539</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43539</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43544</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43558</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>43558</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43560</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43560</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43565</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43570</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>43584</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>43616</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>43621</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>43630</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>43636</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>43643</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>43643</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>43655</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43659</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43661</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43661</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43661</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>43668</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43669</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43669</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43669</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43675</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43676</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43676</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43678</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43679</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>43679</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>43684</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>43688</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>43688</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>43691</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>43717</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>43721</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>43725</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>43726</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43730</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43738</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>43739</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>43740</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>43745</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>43746</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>43747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43752</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43752</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>43753</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>43756</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43758</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43758</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>43762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43769</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43776</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43776</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>43776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43787</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43794</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>43795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>43798</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43803</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>43811</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>43811</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>43811</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>43823</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>43832</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>43834</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>43834</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>43839</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>43846</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>43847</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>43847</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>43853</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>43857</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>43864</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>43872</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>43873</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>43881</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>43885</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>43885</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>43888</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>43889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>43889</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>43893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>43894</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>43901</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>43901</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>43901</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>43902</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43902</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43907</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43907</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43911</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43917</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43920</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43922</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43943</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43948</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43955</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43955</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43957</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43958</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43959</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43959</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43959</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43980</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>43983</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>43983</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>43983</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>43985</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>43998</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>43999</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44007</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44011</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44011</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44015</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44018</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44021</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44023</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44026</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44029</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44039</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44039</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44040</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44042</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44043</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44043</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44047</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44049</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44049</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44053</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44053</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44054</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44054</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44056</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44057</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44061</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44085</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44085</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44085</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44089</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44097</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44098</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44104</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44106</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44109</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44109</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44113</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44123</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44127</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44127</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44138</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44138</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44139</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44140</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44145</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44146</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44152</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44158</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44158</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44160</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44172</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44178</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44187</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44188</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44193</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44201</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44203</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44208</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44208</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44208</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44218</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44230</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44237</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44242</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44242</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44242</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44246</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44246</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44248</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44250</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44250</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44252</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44252</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44260</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44260</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44260</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44263</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44263</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44265</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44270</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44281</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44285</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44292</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44292</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44293</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44297</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44297</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44301</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44301</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>44302</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44302</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44302</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44307</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44309</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44323</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44323</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44328</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44350</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44350</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44358</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44360</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44360</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44360</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44365</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44365</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44365</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44371</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44379</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44381</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44381</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44384</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44386</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>44391</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44411</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44413</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44414</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44414</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>44421</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44423</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44423</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44425</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44425</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44431</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44433</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44435</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44448</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44448</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44448</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44449</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44449</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44449</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44450</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44452</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44453</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44453</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44454</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44458</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44458</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44463</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44466</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44472</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>44473</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44484</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44487</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44495</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44495</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44508</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44508</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44511</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44518</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44522</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>44522</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44524</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44531</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44535</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44536</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44553</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44566</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44571</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44572</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44579</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44580</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44580</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44596</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44596</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44604</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44608</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44610</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44610</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44616</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44624</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44624</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44636</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44636</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44636</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44637</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44637</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44640</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44643</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44643</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44643</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44671</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44671</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44676</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44680</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44697</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44697</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44701</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44715</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44715</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44720</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44722</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44722</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44724</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44725</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44733</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44742</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44745</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44745</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44746</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44752</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44752</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44752</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44753</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>44761</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44769</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44769</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44770</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44771</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44774</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44782</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44785</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44785</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44785</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44791</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44795</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44796</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44803</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44807</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44807</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44814</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44817</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44818</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44818</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44818</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44823</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>44826</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44830</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44834</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>44837</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44838</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44838</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44838</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44848</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44848</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44848</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44854</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44854</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44859</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44859</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>44864</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44868</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44872</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44873</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44881</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44887</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44887</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44887</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44895</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44895</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>44897</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44897</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44899</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44899</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44900</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44900</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44902</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44907</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>44907</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44907</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44908</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44909</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44909</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44909</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44911</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44911</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44914</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>44917</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>44931</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>44942</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44943</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>44953</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44957</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44957</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44958</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44958</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44960</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44966</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44977</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44977</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44979</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44979</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44980</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44985</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44985</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44986</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>44988</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44991</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44991</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44998</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45001</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45001</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45007</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45007</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45012</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45013</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45014</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45014</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45014</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>45016</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45022</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45022</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45022</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45029</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45030</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45030</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45034</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45036</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45036</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45039</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45039</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45039</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45041</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45043</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45048</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45053</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45056</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45056</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45056</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45057</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45065</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45066</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45068</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45070</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45073</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45073</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45079</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45081</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45081</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45082</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45091</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45098</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45098</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45103</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45103</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45104</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45104</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45105</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45105</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45110</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45110</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45112</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45113</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45114</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45114</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45114</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45118</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45119</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45121</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45121</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45121</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45140</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45140</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45140</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45141</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45141</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45142</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45147</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45148</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45154</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45155</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45156</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45156</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45159</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45159</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45160</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45160</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45160</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45161</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45161</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45161</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45162</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45163</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45163</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45163</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45166</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45166</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45168</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45169</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45169</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45169</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45170</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45174</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45175</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45175</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45176</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45180</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45182</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45182</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45182</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45183</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45183</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45187</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45189</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45189</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45191</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45191</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45191</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45192</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45193</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45193</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45195</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45195</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45195</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45196</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45196</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45196</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45205</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45205</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45205</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45209</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45211</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45212</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45212</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45213</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45213</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45214</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45214</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45215</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45215</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45216</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45218</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45222</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45224</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45225</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45225</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45225</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45226</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45228</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45228</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45230</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>45230</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45230</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45231</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45231</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45243</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45243</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45250</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45250</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45251</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45252</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45253</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45256</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>45256</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45256</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45257</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45264</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45264</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45266</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45268</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45268</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45270</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45271</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45272</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45272</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45278</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45280</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45299</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45299</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45299</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45302</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45303</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45303</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45306</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45309</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45311</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45311</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45311</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45314</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59280,14 +59280,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 2930-2024</t>
+          <t>A 2968-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59299,8 +59299,13 @@
           <t>FLEN</t>
         </is>
       </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G970" t="n">
-        <v>2.2</v>
+        <v>10.3</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59344,7 +59349,7 @@
         <v>45315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59394,14 +59399,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 2968-2024</t>
+          <t>A 2930-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59413,13 +59418,8 @@
           <t>FLEN</t>
         </is>
       </c>
-      <c r="F972" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G972" t="n">
-        <v>10.3</v>
+        <v>2.2</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -59463,7 +59463,7 @@
         <v>45320</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45321</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45321</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45321</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45322</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45322</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45323</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45323</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45323</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45327</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45327</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60083,14 +60083,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 4724-2024</t>
+          <t>A 4657-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -60140,14 +60140,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 4657-2024</t>
+          <t>A 4724-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60160,7 +60160,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -60204,7 +60204,7 @@
         <v>45328</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60261,7 +60261,7 @@
         <v>45330</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45330</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45331</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60435,14 +60435,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 6109-2024</t>
+          <t>A 6104-2024</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -60492,14 +60492,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 6104-2024</t>
+          <t>A 6109-2024</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60512,7 +60512,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -60556,7 +60556,7 @@
         <v>45341</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45343</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
       </c>
       <c r="R993" s="2" t="inlineStr"/>
     </row>
-    <row r="994">
+    <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
           <t>A 6982-2024</t>
@@ -60670,7 +60670,7 @@
         <v>45343</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60716,6 +60716,234 @@
         <v>0</v>
       </c>
       <c r="R994" s="2" t="inlineStr"/>
+    </row>
+    <row r="995" ht="15" customHeight="1">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>A 7376-2024</t>
+        </is>
+      </c>
+      <c r="B995" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C995" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G995" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H995" t="n">
+        <v>0</v>
+      </c>
+      <c r="I995" t="n">
+        <v>0</v>
+      </c>
+      <c r="J995" t="n">
+        <v>0</v>
+      </c>
+      <c r="K995" t="n">
+        <v>0</v>
+      </c>
+      <c r="L995" t="n">
+        <v>0</v>
+      </c>
+      <c r="M995" t="n">
+        <v>0</v>
+      </c>
+      <c r="N995" t="n">
+        <v>0</v>
+      </c>
+      <c r="O995" t="n">
+        <v>0</v>
+      </c>
+      <c r="P995" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q995" t="n">
+        <v>0</v>
+      </c>
+      <c r="R995" s="2" t="inlineStr"/>
+    </row>
+    <row r="996" ht="15" customHeight="1">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>A 7380-2024</t>
+        </is>
+      </c>
+      <c r="B996" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C996" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G996" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H996" t="n">
+        <v>0</v>
+      </c>
+      <c r="I996" t="n">
+        <v>0</v>
+      </c>
+      <c r="J996" t="n">
+        <v>0</v>
+      </c>
+      <c r="K996" t="n">
+        <v>0</v>
+      </c>
+      <c r="L996" t="n">
+        <v>0</v>
+      </c>
+      <c r="M996" t="n">
+        <v>0</v>
+      </c>
+      <c r="N996" t="n">
+        <v>0</v>
+      </c>
+      <c r="O996" t="n">
+        <v>0</v>
+      </c>
+      <c r="P996" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q996" t="n">
+        <v>0</v>
+      </c>
+      <c r="R996" s="2" t="inlineStr"/>
+    </row>
+    <row r="997" ht="15" customHeight="1">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>A 7381-2024</t>
+        </is>
+      </c>
+      <c r="B997" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C997" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G997" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H997" t="n">
+        <v>0</v>
+      </c>
+      <c r="I997" t="n">
+        <v>0</v>
+      </c>
+      <c r="J997" t="n">
+        <v>0</v>
+      </c>
+      <c r="K997" t="n">
+        <v>0</v>
+      </c>
+      <c r="L997" t="n">
+        <v>0</v>
+      </c>
+      <c r="M997" t="n">
+        <v>0</v>
+      </c>
+      <c r="N997" t="n">
+        <v>0</v>
+      </c>
+      <c r="O997" t="n">
+        <v>0</v>
+      </c>
+      <c r="P997" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q997" t="n">
+        <v>0</v>
+      </c>
+      <c r="R997" s="2" t="inlineStr"/>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>A 7378-2024</t>
+        </is>
+      </c>
+      <c r="B998" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C998" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G998" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H998" t="n">
+        <v>0</v>
+      </c>
+      <c r="I998" t="n">
+        <v>0</v>
+      </c>
+      <c r="J998" t="n">
+        <v>0</v>
+      </c>
+      <c r="K998" t="n">
+        <v>0</v>
+      </c>
+      <c r="L998" t="n">
+        <v>0</v>
+      </c>
+      <c r="M998" t="n">
+        <v>0</v>
+      </c>
+      <c r="N998" t="n">
+        <v>0</v>
+      </c>
+      <c r="O998" t="n">
+        <v>0</v>
+      </c>
+      <c r="P998" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q998" t="n">
+        <v>0</v>
+      </c>
+      <c r="R998" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>43363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43558</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43661</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>43703</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>43747</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>43754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43776</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43858</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43860</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43943</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43957</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44014</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44127</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44474</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44484</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44503</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44533</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44608</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44624</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44637</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44735</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44792</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44798</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44854</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44865</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44911</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44931</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44956</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44957</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44971</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44986</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45156</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45166</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45212</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45219</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45323</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45337</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43324</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43334</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43347</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43347</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43357</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43368</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>43370</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43374</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43388</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43388</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43395</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43397</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43404</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43410</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43412</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43423</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>43424</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43433</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43437</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43455</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43472</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43476</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43494</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43497</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43503</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43514</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43522</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43530</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43530</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43535</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43538</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43539</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43539</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43544</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43558</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>43558</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43560</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43560</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43565</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43570</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>43584</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>43616</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>43621</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>43630</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>43636</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>43643</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>43643</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>43655</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43659</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43661</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43661</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43661</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>43668</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43669</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43669</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43669</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43675</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43676</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43676</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43678</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43679</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>43679</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>43684</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>43688</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>43688</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>43691</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>43717</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>43721</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>43725</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>43726</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43730</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43738</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>43739</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>43740</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>43745</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>43746</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>43747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43752</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43752</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>43753</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>43756</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43758</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43758</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>43762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43769</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43776</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43776</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>43776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43787</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43794</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>43795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>43798</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43803</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>43811</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>43811</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>43811</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>43823</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>43832</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>43834</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>43834</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>43839</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>43846</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>43847</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>43847</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>43853</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>43857</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>43864</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>43872</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>43873</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>43881</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>43885</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>43885</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>43888</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>43889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>43889</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>43893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>43894</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>43901</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>43901</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>43901</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>43902</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43902</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43907</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43907</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43911</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43917</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43920</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43922</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43943</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43948</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43955</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43955</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43957</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43958</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43959</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43959</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43959</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43980</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>43983</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>43983</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>43983</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>43985</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>43998</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>43999</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44007</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44011</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44011</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44015</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44018</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44021</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44023</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44026</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44029</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44039</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44039</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44040</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44042</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44043</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44043</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44047</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44049</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44049</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44053</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44053</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44054</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44054</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44056</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44057</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44061</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44085</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44085</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44085</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44089</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44097</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44098</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44104</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44106</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44109</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44109</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44113</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44123</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44127</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44127</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44138</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44138</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44139</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44140</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44145</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44146</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44152</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44158</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44158</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44160</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44172</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44178</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44187</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44188</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44193</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44201</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44203</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44208</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44208</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44208</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44218</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44230</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44237</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44242</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44242</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44242</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44246</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44246</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44248</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44250</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44250</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44252</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44252</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44260</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44260</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44260</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44263</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44263</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44265</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44270</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44281</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44285</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44292</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44292</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44293</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44297</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44297</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44301</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44301</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>44302</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44302</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44302</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44307</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44309</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44323</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44323</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44328</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44350</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44350</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44358</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44360</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44360</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44360</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44365</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44365</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44365</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44371</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44379</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44381</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44381</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44384</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44386</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>44391</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44411</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44413</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44414</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44414</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>44421</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44423</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44423</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44425</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44425</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44431</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44433</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44435</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44448</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44448</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44448</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44449</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44449</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44449</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44450</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44452</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44453</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44453</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44454</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44458</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44458</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44463</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44466</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44472</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>44473</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44484</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44487</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44495</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44495</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44508</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44508</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44511</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44518</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44522</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>44522</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44524</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44531</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44535</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44536</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44553</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44566</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44571</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44572</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44579</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44580</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44580</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44596</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44596</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44604</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44608</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44610</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44610</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44616</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44624</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44624</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44636</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44636</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44636</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44637</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44637</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44640</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44643</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44643</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44643</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44671</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44671</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44676</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44680</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44697</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44697</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44701</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44715</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44715</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44720</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44722</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44722</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44724</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44725</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44733</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44742</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44745</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44745</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44746</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44752</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44752</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44752</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44753</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>44761</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44769</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44769</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44770</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44771</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44774</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44782</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44785</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44785</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44785</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44791</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44795</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44796</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44803</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44807</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44807</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44814</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44817</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44818</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44818</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44818</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44823</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>44826</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44830</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44834</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>44837</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44838</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44838</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44838</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44848</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44848</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44848</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44854</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44854</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44859</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44859</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>44864</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44868</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44872</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44873</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44881</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44887</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44887</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44887</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44895</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44895</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>44897</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44897</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44899</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44899</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44900</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44900</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44902</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44907</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>44907</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44907</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44908</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44909</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44909</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44909</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44911</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44911</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44914</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>44917</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>44931</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>44942</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44943</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>44953</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44957</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44957</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44958</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44958</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44960</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44966</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44977</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44977</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44979</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44979</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44980</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44985</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44985</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44986</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>44988</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44991</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44991</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44998</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45001</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45001</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45007</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45007</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45012</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45013</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45014</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45014</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45014</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>45016</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45022</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45022</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45022</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45029</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45030</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45030</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45034</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45036</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45036</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45039</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45039</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45039</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45041</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45043</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45048</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45053</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45056</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45056</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45056</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45057</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45065</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45066</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45068</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45070</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45073</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45073</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45079</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45081</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45081</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45082</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45091</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45098</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45098</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45103</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45103</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45104</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45104</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45105</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45105</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45110</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45110</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45112</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45113</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45114</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45114</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45114</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45118</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45119</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45121</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45121</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45121</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45140</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45140</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45140</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45141</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45141</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45142</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45147</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45148</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45154</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45155</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45156</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45156</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45159</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45159</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45160</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45160</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45160</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45161</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45161</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45161</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45162</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45163</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45163</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45163</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45166</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45166</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45168</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45169</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45169</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45169</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45170</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45174</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45175</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45175</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45176</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45180</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45182</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45182</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45182</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45183</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45183</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45187</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45189</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45189</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45191</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45191</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45191</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45192</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45193</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45193</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45195</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45195</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45195</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45196</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45196</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45196</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45205</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45205</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45205</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45209</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45211</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45212</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45212</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45213</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45213</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45214</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45214</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45215</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45215</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45216</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45218</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45222</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45224</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45225</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45225</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45225</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45226</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45228</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45228</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45230</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>45230</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45230</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45231</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45231</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45243</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45243</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45250</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45250</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45251</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45252</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45253</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45256</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>45256</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45256</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45257</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45264</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45264</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45266</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45268</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45268</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45270</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45271</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45272</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45272</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45278</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45280</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45299</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45299</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45299</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45302</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45303</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45303</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45306</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45309</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45311</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45311</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45311</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45314</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45315</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45315</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45320</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45321</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59570,14 +59570,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 3774-2024</t>
+          <t>A 3798-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59627,14 +59627,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 3798-2024</t>
+          <t>A 3774-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59647,7 +59647,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -59684,14 +59684,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 3926-2024</t>
+          <t>A 3909-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59741,14 +59741,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 3909-2024</t>
+          <t>A 3926-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59805,7 +59805,7 @@
         <v>45323</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45323</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45323</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45327</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45327</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>45328</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60140,14 +60140,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 4724-2024</t>
+          <t>A 4778-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60160,7 +60160,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -60197,14 +60197,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 4778-2024</t>
+          <t>A 4724-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -60254,14 +60254,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 5160-2024</t>
+          <t>A 5194-2024</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60279,7 +60279,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -60316,14 +60316,14 @@
     <row r="988" ht="15" customHeight="1">
       <c r="A988" t="inlineStr">
         <is>
-          <t>A 5194-2024</t>
+          <t>A 5160-2024</t>
         </is>
       </c>
       <c r="B988" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         </is>
       </c>
       <c r="G988" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H988" t="n">
         <v>0</v>
@@ -60385,7 +60385,7 @@
         <v>45331</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60435,14 +60435,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 6104-2024</t>
+          <t>A 6109-2024</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -60492,14 +60492,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 6109-2024</t>
+          <t>A 6104-2024</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60512,7 +60512,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -60556,7 +60556,7 @@
         <v>45341</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45343</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45343</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45345</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>45345</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60834,14 +60834,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 7381-2024</t>
+          <t>A 7378-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -60891,14 +60891,14 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 7378-2024</t>
+          <t>A 7381-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>43363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43558</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43661</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>43703</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>43747</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>43754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43776</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43858</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43860</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43943</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43957</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44014</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44127</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44474</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44484</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44503</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44533</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44608</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44624</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44637</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44735</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44792</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44798</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44854</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44865</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44911</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44931</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44956</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44957</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44971</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44986</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45156</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45166</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45212</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45219</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45323</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45337</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43324</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43334</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43347</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43347</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43357</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43368</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>43370</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43374</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43388</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43388</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43395</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43397</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43404</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43410</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43412</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43423</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>43424</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43433</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43437</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43455</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43472</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43476</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43494</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43497</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43503</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43514</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43522</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43530</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43530</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43535</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43538</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43539</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43539</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43544</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43558</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>43558</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43560</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43560</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43565</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43570</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>43584</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>43616</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>43621</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>43630</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>43636</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>43643</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>43643</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>43655</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43659</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43661</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43661</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43661</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>43668</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43669</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43669</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43669</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43675</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43676</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43676</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43678</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43679</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>43679</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>43684</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>43688</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>43688</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>43691</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>43717</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>43721</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>43725</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>43726</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43730</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43738</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>43739</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>43740</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>43745</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>43746</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>43747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43752</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43752</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>43753</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>43756</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43758</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43758</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>43762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43769</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43776</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43776</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>43776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43787</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43794</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>43795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>43798</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43803</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>43811</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>43811</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>43811</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>43823</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>43832</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>43834</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>43834</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>43839</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>43846</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>43847</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>43847</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>43853</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>43857</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>43864</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>43872</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>43873</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>43881</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>43885</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>43885</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>43888</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>43889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>43889</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>43893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>43894</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>43901</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>43901</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>43901</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>43902</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43902</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43907</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43907</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43911</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43917</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43920</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43922</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43943</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43948</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43955</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43955</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43957</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43958</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43959</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43959</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43959</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43980</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>43983</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>43983</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>43983</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>43985</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>43998</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>43999</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44007</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44011</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44011</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44015</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44018</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44021</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44023</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44026</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44029</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44039</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44039</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44040</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44042</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44043</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44043</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44047</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44049</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44049</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44053</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44053</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44054</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44054</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44056</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44057</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44061</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44085</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44085</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44085</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44089</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44097</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44098</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44104</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44106</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44109</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44109</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44113</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44123</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44127</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44127</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44138</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44138</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44139</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44140</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44145</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44146</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44152</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44158</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44158</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44160</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44172</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44178</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44187</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44188</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44193</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44201</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44203</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44208</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44208</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44208</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44218</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44230</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44237</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44242</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44242</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44242</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44246</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44246</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44248</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44250</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44250</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44252</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44252</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44260</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44260</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44260</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44263</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44263</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44265</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44270</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44281</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44285</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44292</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44292</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44293</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44297</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44297</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44301</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44301</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>44302</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44302</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44302</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44307</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44309</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44323</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44323</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44328</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44350</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44350</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44358</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44360</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44360</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44360</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44365</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44365</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44365</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44371</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44379</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44381</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44381</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44384</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44386</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>44391</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44411</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44413</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44414</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44414</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>44421</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44423</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44423</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44425</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44425</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44431</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44433</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44435</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44448</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44448</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44448</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44449</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44449</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44449</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44450</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44452</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44453</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44453</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44454</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44458</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44458</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44463</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44466</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44472</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>44473</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44484</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44487</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44495</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44495</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44508</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44508</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44511</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44518</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44522</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>44522</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44524</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44531</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44535</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44536</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44553</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44566</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44571</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44572</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44579</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44580</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44580</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44596</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44596</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44604</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44608</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44610</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44610</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44616</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44624</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44624</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44636</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44636</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44636</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44637</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44637</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44640</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44643</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44643</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44643</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44671</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44671</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44676</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44680</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44697</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44697</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44701</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44715</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44715</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44720</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44722</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44722</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44724</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44725</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44733</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44742</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44745</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44745</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44746</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44752</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44752</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44752</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44753</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>44761</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44769</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44769</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44770</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44771</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44774</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44782</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44785</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44785</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44785</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44791</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44795</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44796</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44803</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44807</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44807</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44814</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44817</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44818</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44818</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44818</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44823</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>44826</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44830</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44834</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>44837</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44838</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44838</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44838</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44848</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44848</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44848</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44854</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44854</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44859</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44859</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>44864</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44868</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44872</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44873</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44881</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44887</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44887</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44887</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44895</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44895</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>44897</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44897</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44899</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44899</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44900</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44900</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44902</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44907</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>44907</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44907</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44908</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44909</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44909</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44909</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44911</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44911</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44914</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>44917</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>44931</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>44942</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44943</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>44953</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44957</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44957</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44958</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44958</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44960</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44966</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44977</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44977</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44979</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44979</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44980</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44985</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44985</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44986</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>44988</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44991</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44991</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44998</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45001</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45001</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45007</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45007</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45012</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45013</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45014</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45014</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45014</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>45016</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45022</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45022</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45022</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45029</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45030</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45030</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45034</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45036</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45036</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45039</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45039</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45039</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45041</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45043</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45048</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45053</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45056</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45056</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45056</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45057</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45065</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45066</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45068</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45070</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45073</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45073</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45079</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45081</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45081</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45082</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45091</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45098</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45098</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45103</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45103</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45104</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45104</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45105</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45105</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45110</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45110</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45112</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45113</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45114</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45114</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45114</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45118</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45119</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45121</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45121</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45121</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45140</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45140</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45140</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45141</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45141</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45142</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45147</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45148</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45154</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45155</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45156</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45156</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45159</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45159</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45160</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45160</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45160</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45161</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45161</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45161</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45162</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45163</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45163</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45163</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45166</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45166</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45168</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45169</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45169</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45169</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45170</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45174</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45175</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45175</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45176</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45180</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45182</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45182</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45182</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45183</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45183</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45187</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45189</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45189</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45191</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45191</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45191</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45192</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45193</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45193</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45195</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45195</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45195</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45196</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45196</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45196</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45205</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45205</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45205</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45209</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45211</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45212</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45212</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45213</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45213</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45214</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45214</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45215</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45215</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45216</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45218</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45222</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45224</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45225</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45225</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45225</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45226</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45228</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45228</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45230</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>45230</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45230</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45231</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45231</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45243</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45243</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45250</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45250</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45251</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45252</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45253</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45256</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>45256</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45256</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45257</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45264</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45264</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45266</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45268</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45268</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45270</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45271</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45272</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45272</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45278</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45280</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45299</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45299</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45299</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45302</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45303</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45303</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45306</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45309</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45311</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45311</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45311</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45314</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45315</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45315</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45320</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45321</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45321</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45321</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59684,14 +59684,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 3909-2024</t>
+          <t>A 3926-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59741,14 +59741,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 3926-2024</t>
+          <t>A 3909-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59798,14 +59798,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 4015-2024</t>
+          <t>A 4143-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59818,7 +59818,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -59855,14 +59855,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 4143-2024</t>
+          <t>A 4147-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59875,7 +59875,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -59912,14 +59912,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 4147-2024</t>
+          <t>A 4015-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59932,7 +59932,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -59976,7 +59976,7 @@
         <v>45327</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45327</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60083,14 +60083,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 4657-2024</t>
+          <t>A 4724-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -60147,7 +60147,7 @@
         <v>45328</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60197,14 +60197,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 4724-2024</t>
+          <t>A 4657-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -60254,14 +60254,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 5194-2024</t>
+          <t>A 5160-2024</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60279,7 +60279,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -60316,14 +60316,14 @@
     <row r="988" ht="15" customHeight="1">
       <c r="A988" t="inlineStr">
         <is>
-          <t>A 5160-2024</t>
+          <t>A 5194-2024</t>
         </is>
       </c>
       <c r="B988" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         </is>
       </c>
       <c r="G988" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="H988" t="n">
         <v>0</v>
@@ -60385,7 +60385,7 @@
         <v>45331</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60435,14 +60435,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 6109-2024</t>
+          <t>A 6104-2024</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -60492,14 +60492,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 6104-2024</t>
+          <t>A 6109-2024</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60512,7 +60512,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -60556,7 +60556,7 @@
         <v>45341</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45343</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45343</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60720,14 +60720,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 7376-2024</t>
+          <t>A 7378-2024</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -60777,14 +60777,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 7380-2024</t>
+          <t>A 7376-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -60834,14 +60834,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 7378-2024</t>
+          <t>A 7380-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -60898,7 +60898,7 @@
         <v>45345</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z998"/>
+  <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>43363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43558</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43661</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>43703</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>43747</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>43754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43776</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43858</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43860</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43943</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43957</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44014</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44127</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44474</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44484</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44503</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44533</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44608</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44624</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44637</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44735</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44792</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44798</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44854</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44865</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44911</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44931</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44956</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44957</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44971</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44986</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45156</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45166</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45212</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45219</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45323</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45337</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43324</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43334</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43347</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43347</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43357</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43368</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>43370</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43374</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43388</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43388</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43395</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43397</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43404</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43410</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43412</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43423</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>43424</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43433</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43437</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43455</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43472</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43476</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43494</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43497</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43503</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43514</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43522</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43530</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43530</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43535</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43538</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43539</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43539</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43544</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43558</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>43558</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43560</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43560</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43565</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43570</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>43584</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>43616</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>43621</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>43630</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>43636</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>43643</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>43643</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>43655</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43659</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43661</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43661</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43661</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>43668</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43669</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43669</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43669</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43675</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43676</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43676</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43678</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43679</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>43679</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>43684</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>43688</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>43688</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>43691</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>43717</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>43721</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>43725</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>43726</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43730</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43738</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>43739</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>43740</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>43745</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>43746</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>43747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43752</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43752</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>43753</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>43756</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43758</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43758</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>43762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43769</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43776</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43776</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>43776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43787</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43794</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>43795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>43798</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43803</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>43811</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>43811</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>43811</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>43823</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>43832</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>43834</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>43834</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>43839</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>43846</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>43847</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>43847</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>43853</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>43857</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>43864</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>43872</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>43873</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>43881</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>43885</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>43885</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>43888</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>43889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>43889</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>43893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>43894</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>43901</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>43901</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>43901</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>43902</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43902</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43907</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43907</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43911</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43917</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43920</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43922</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43943</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43948</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43955</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43955</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43957</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43958</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43959</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43959</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43959</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43980</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>43983</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>43983</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>43983</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>43985</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>43998</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>43999</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44007</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44011</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44011</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44015</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44018</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44021</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44023</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44026</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44029</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44039</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44039</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44040</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44042</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44043</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44043</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44047</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44049</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44049</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44053</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44053</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44054</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44054</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44056</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44057</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44061</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44085</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44085</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44085</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44089</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44097</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44098</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44104</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44106</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44109</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44109</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44113</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44123</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44127</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44127</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44138</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44138</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44139</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44140</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44145</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44146</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44152</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44158</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44158</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44160</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44172</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44178</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44187</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44188</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44193</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44201</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44203</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44208</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44208</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44208</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44218</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44230</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44237</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44242</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44242</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44242</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44246</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44246</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44248</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44250</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44250</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44252</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44252</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44260</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44260</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44260</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44263</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44263</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44265</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44270</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44281</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44285</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44292</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44292</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44293</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44297</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44297</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44301</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44301</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>44302</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44302</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44302</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44307</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44309</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44323</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44323</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44328</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44350</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44350</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44358</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44360</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44360</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44360</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44365</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44365</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44365</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44371</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44379</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44381</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44381</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44384</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44386</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>44391</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44411</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44413</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44414</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44414</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>44421</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44423</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44423</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44425</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44425</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44431</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44433</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44435</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44448</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44448</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44448</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44449</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44449</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44449</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44450</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44452</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44453</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44453</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44454</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44458</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44458</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44463</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44466</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44472</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>44473</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44484</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44487</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44495</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44495</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44508</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44508</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44511</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44518</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44522</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>44522</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44524</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44531</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44535</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44536</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44553</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44566</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44571</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44572</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44579</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44580</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44580</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44596</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44596</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44604</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44608</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44610</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44610</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44616</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44624</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44624</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44636</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44636</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44636</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44637</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44637</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44640</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44643</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44643</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44643</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44671</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44671</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44676</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44680</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44697</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44697</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44701</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44715</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44715</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44720</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44722</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44722</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44724</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44725</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44733</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44742</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44745</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44745</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44746</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44752</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44752</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44752</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44753</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>44761</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44769</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44769</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44770</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44771</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44774</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44782</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44785</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44785</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44785</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44791</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44795</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44796</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44803</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44807</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44807</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44814</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44817</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44818</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44818</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44818</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44823</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>44826</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44830</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44834</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>44837</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44838</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44838</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44838</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44848</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44848</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44848</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44854</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44854</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44859</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44859</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>44864</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44868</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44872</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44873</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44881</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44887</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44887</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44887</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44895</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44895</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>44897</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44897</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44899</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44899</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44900</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44900</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44902</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44907</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>44907</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44907</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44908</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44909</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44909</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44909</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44911</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44911</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44914</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>44917</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>44931</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>44942</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44943</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>44953</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44957</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44957</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44958</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44958</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44960</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44966</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44977</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44977</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44979</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44979</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44980</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44985</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44985</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44986</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>44988</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44991</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44991</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44998</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45001</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45001</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45007</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45007</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45012</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45013</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45014</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45014</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45014</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>45016</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45022</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45022</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45022</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45029</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45030</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45030</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45034</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45036</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45036</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45039</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45039</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45039</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45041</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45043</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45048</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45053</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45056</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45056</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45056</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45057</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45065</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45066</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45068</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45070</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45073</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45073</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45079</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45081</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45081</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45082</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45091</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45098</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45098</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45103</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45103</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45104</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45104</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45105</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45105</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45110</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45110</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45112</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45113</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45114</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45114</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45114</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45118</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45119</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45121</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45121</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45121</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45140</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45140</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45140</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45141</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45141</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45142</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45147</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45148</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45154</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45155</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45156</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45156</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45159</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45159</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45160</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45160</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45160</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45161</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45161</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45161</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45162</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45163</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45163</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45163</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45166</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45166</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45168</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45169</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45169</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45169</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45170</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45174</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45175</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45175</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45176</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45180</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45182</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45182</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45182</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45183</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45183</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45187</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45189</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45189</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45191</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45191</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45191</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45192</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45193</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45193</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45195</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45195</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45195</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45196</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45196</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45196</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45205</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45205</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45205</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45209</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45211</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45212</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45212</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45213</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45213</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45214</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45214</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45215</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45215</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45216</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45218</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45222</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45224</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45225</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45225</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45225</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45226</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45228</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45228</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45230</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>45230</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45230</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45231</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45231</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45243</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45243</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45250</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45250</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45251</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45252</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45253</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45256</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>45256</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45256</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45257</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45264</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45264</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45266</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45268</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45268</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45270</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45271</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45272</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45272</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45278</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45280</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45299</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45299</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45299</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45302</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45303</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45303</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45306</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45309</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45311</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45311</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45311</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45314</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45315</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45315</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45320</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45321</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59570,14 +59570,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 3798-2024</t>
+          <t>A 3774-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59627,14 +59627,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 3774-2024</t>
+          <t>A 3798-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59647,7 +59647,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -59684,14 +59684,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 3926-2024</t>
+          <t>A 3909-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59741,14 +59741,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 3909-2024</t>
+          <t>A 3926-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59798,14 +59798,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 4143-2024</t>
+          <t>A 4015-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59818,7 +59818,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -59855,14 +59855,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 4147-2024</t>
+          <t>A 4143-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59875,7 +59875,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -59912,14 +59912,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 4015-2024</t>
+          <t>A 4147-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59932,7 +59932,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -59976,7 +59976,7 @@
         <v>45327</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45327</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60083,14 +60083,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 4724-2024</t>
+          <t>A 4657-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -60147,7 +60147,7 @@
         <v>45328</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60197,14 +60197,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 4657-2024</t>
+          <t>A 4724-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -60261,7 +60261,7 @@
         <v>45330</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45330</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45331</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60442,7 +60442,7 @@
         <v>45337</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45337</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>45341</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45343</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45343</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45345</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>45345</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60841,7 +60841,7 @@
         <v>45345</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
       </c>
       <c r="R997" s="2" t="inlineStr"/>
     </row>
-    <row r="998">
+    <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
           <t>A 7381-2024</t>
@@ -60898,7 +60898,7 @@
         <v>45345</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60944,6 +60944,120 @@
         <v>0</v>
       </c>
       <c r="R998" s="2" t="inlineStr"/>
+    </row>
+    <row r="999" ht="15" customHeight="1">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>A 7526-2024</t>
+        </is>
+      </c>
+      <c r="B999" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C999" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G999" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H999" t="n">
+        <v>0</v>
+      </c>
+      <c r="I999" t="n">
+        <v>0</v>
+      </c>
+      <c r="J999" t="n">
+        <v>0</v>
+      </c>
+      <c r="K999" t="n">
+        <v>0</v>
+      </c>
+      <c r="L999" t="n">
+        <v>0</v>
+      </c>
+      <c r="M999" t="n">
+        <v>0</v>
+      </c>
+      <c r="N999" t="n">
+        <v>0</v>
+      </c>
+      <c r="O999" t="n">
+        <v>0</v>
+      </c>
+      <c r="P999" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q999" t="n">
+        <v>0</v>
+      </c>
+      <c r="R999" s="2" t="inlineStr"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>A 7525-2024</t>
+        </is>
+      </c>
+      <c r="B1000" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C1000" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>FLEN</t>
+        </is>
+      </c>
+      <c r="G1000" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1000" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>43363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43558</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43661</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>43703</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>43747</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>43754</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43776</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43858</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43860</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43943</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43957</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44014</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44127</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44474</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44484</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44503</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44533</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44608</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44624</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44637</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44735</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44792</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44798</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44854</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44865</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44911</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44931</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44956</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44957</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44971</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44986</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45156</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45166</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45212</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45219</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45323</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45337</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43324</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43334</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43347</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43347</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43357</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43368</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>43370</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43374</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43388</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43388</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43395</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43397</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43404</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43410</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43412</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43423</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>43424</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43433</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43437</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43455</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43472</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43476</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43494</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43497</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43503</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43514</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43522</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43530</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43530</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43535</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43538</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43539</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43539</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43544</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43551</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43558</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>43558</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43560</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43560</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43565</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43570</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>43584</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>43616</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>43621</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>43630</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>43636</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>43643</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>43643</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>43655</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43659</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43661</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43661</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43661</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>43668</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43669</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43669</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43669</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43675</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43676</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43676</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43678</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43679</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>43679</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>43684</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>43688</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>43688</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>43691</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>43717</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>43721</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>43725</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>43726</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43730</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43738</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>43739</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>43740</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>43745</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>43746</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>43747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43752</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43752</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>43753</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>43756</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43758</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43758</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>43762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43769</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43776</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43776</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>43776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43787</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43794</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>43795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>43798</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43803</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>43811</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>43811</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>43811</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>43823</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>43832</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>43834</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>43834</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>43839</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>43846</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>43847</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>43847</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>43853</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>43857</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>43864</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>43872</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>43873</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>43881</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>43885</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>43885</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>43888</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>43889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>43889</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>43893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>43894</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>43901</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>43901</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>43901</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>43902</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43902</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43907</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43907</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43911</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43917</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43920</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43922</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43943</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43948</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43955</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43955</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43957</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43958</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43959</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43959</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43959</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43980</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>43983</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>43983</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>43983</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>43985</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>43998</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>43999</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44007</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44011</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44011</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44015</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44018</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44021</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44023</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44026</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44029</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44039</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44039</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44040</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44042</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44043</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44043</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44047</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44049</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44049</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44053</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44053</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44054</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44054</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44056</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44057</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44061</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44085</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44085</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44085</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44089</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44097</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44098</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44104</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44106</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44109</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44109</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44113</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44123</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44127</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44127</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44138</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44138</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44139</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44140</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44145</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44146</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44152</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44158</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44158</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44160</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44172</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44178</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44187</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44188</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44193</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44201</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44203</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44208</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44208</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44208</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44214</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44218</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44230</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44237</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44242</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44242</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44242</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44246</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44246</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44248</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44250</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44250</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44252</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44252</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44260</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44260</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44260</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44263</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44263</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44265</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44270</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44281</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44285</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44292</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44292</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44293</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44297</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44297</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44301</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44301</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>44302</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44302</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44302</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44307</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44309</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44323</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44323</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44328</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44350</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44350</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44358</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44360</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44360</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44360</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44365</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44365</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44365</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44371</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44379</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44381</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44381</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44384</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44386</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>44391</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44411</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44413</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44414</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44414</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>44421</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44423</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44423</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44425</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44425</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44431</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44433</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44435</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44448</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44448</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44448</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44449</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44449</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44449</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44450</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44452</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44453</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44453</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44454</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44458</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44458</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44463</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44463</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44466</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44472</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>44473</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44484</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44487</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44490</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44495</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44495</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44501</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44508</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44508</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44511</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44518</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44522</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>44522</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44524</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44531</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44535</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44536</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44553</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44566</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44571</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44572</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44579</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44580</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44580</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44596</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44596</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44604</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44608</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44610</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44610</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44614</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44616</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44624</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44624</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44636</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44636</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44636</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44637</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44637</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44640</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44643</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44643</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44643</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44671</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44671</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44676</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44680</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44697</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44697</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44701</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44715</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44715</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44720</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44722</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44722</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44724</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44725</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44733</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44742</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44745</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44745</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44746</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44752</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44752</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44752</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44753</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>44761</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44769</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44769</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44770</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44771</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44774</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44782</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44785</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44785</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44785</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44791</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44795</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44796</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44803</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44807</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44807</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44814</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44817</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44818</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44818</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44818</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44823</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>44826</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44830</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44834</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>44837</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44838</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44838</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44838</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44846</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44848</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44848</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44848</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44854</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44854</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44859</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44859</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>44864</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44868</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44872</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44873</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44881</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44887</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44887</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44887</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44895</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44895</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>44897</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44897</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44899</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44899</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44900</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44900</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44902</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44907</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>44907</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44907</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44908</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44909</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44909</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44909</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44911</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44911</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44914</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>44917</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>44931</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>44942</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44943</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>44953</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44957</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44957</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44958</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44958</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44960</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44966</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44977</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44977</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44979</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44979</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44980</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44985</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44985</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44986</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>44988</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44991</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44991</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44998</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45001</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45001</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45007</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45007</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45008</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45012</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45013</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45014</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45014</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45014</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>45016</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45022</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45022</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45022</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45029</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45030</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45030</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45034</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45036</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45036</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45039</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45039</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45039</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45041</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45043</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45048</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45053</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45056</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45056</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45056</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45057</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45065</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45066</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45068</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45070</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45073</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45073</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45079</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45081</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45081</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45082</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45091</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45098</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45098</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45103</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45103</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45104</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45104</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45105</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45105</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45105</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45110</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45110</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45112</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45113</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45114</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45114</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45114</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45118</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45119</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45121</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45121</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45121</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45140</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45140</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45140</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45141</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45141</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45142</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45147</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45147</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45147</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45148</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45149</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45154</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45155</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45156</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45156</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45159</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45159</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45160</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45160</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45160</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45161</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45161</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45161</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45162</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45163</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45163</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45163</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45166</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45166</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45166</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45168</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45169</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45169</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45169</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45170</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45174</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45175</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45175</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45176</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45180</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45182</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45182</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45182</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45183</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45183</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45187</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45189</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45189</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45191</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45191</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45191</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45192</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45193</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45193</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45195</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45195</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45195</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45196</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45196</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45196</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45205</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45205</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45205</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45209</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45211</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45212</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45212</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45213</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45213</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45214</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45214</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45215</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45215</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45216</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45218</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45222</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45224</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45225</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45225</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45225</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45226</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45228</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45228</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45230</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>45230</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45230</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45231</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45231</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45243</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45243</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45250</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45250</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45251</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45252</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45253</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45256</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>45256</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45256</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45257</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45264</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45264</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45266</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45268</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45268</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45270</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45271</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45272</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45272</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45278</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45280</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45299</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45299</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45299</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45302</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45303</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45303</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45306</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45309</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45311</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45311</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45311</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45314</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45315</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45315</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45315</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45320</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45321</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45321</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45321</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45322</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45322</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45323</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45323</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45323</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45327</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45327</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>45328</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60140,14 +60140,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 4778-2024</t>
+          <t>A 4724-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60160,7 +60160,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -60197,14 +60197,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 4724-2024</t>
+          <t>A 4778-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -60261,7 +60261,7 @@
         <v>45330</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45330</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45331</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60442,7 +60442,7 @@
         <v>45337</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45337</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>45341</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45343</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45343</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45345</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60777,14 +60777,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 7376-2024</t>
+          <t>A 7381-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -60834,14 +60834,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 7380-2024</t>
+          <t>A 7376-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -60891,14 +60891,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 7381-2024</t>
+          <t>A 7380-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -60948,14 +60948,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 7526-2024</t>
+          <t>A 7525-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -61005,14 +61005,14 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 7525-2024</t>
+          <t>A 7526-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45350</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>43363</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>43558</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>43661</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>43691</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>43703</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>43747</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>43754</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>43776</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43858</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>43860</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>43943</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>43957</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44014</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44127</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>44397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>44474</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44484</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>44503</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44533</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>44553</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44608</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44624</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>44637</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44735</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44792</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44798</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>44854</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44865</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44911</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44956</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44957</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>44971</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44986</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45156</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45166</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45209</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45212</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>45219</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>45323</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>45337</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>45350</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43324</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43334</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43347</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43347</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43357</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43368</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43368</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43370</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43371</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43374</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43388</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43388</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43395</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43397</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43404</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43410</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43412</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43423</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43424</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43426</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43437</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43444</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43446</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43450</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43455</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43472</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43483</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43490</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43494</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43495</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>43497</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>43503</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43522</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43522</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43535</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43538</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43539</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43539</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>43544</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>43551</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>43558</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43559</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43559</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43560</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43560</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>43565</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>43567</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>43570</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>43616</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>43621</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>43630</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>43635</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>43636</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43643</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43643</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>43655</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>43659</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>43661</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>43661</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>43661</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>43664</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>43668</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43669</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43669</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43669</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43669</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43675</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43676</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>43676</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>43678</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>43679</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>43679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>43679</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43679</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>43684</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>43688</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>43688</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>43691</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>43696</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>43697</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>43717</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43721</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43725</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>43726</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>43730</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>43738</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>43739</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>43740</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43745</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43746</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43747</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43752</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>43752</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43753</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>43756</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43758</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>43758</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>43762</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>43769</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>43774</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>43776</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>43776</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>43787</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43794</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>43795</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>43798</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43803</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43811</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43811</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>43811</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>43823</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>43832</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>43834</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43834</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>43839</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43846</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43847</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>43847</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>43853</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>43864</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>43872</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>43873</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>43881</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>43885</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>43885</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>43888</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>43889</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>43889</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>43893</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>43901</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>43901</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>43901</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>43902</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>43907</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43907</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43911</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43917</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43920</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43922</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43943</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43948</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43955</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43955</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43957</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43958</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43959</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43959</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>43959</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>43979</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>43980</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>43983</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>43983</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43983</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>43998</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>43999</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>43999</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44004</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44007</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44011</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44011</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44012</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44015</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44018</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44021</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44023</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44026</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44027</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44028</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44029</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44039</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44039</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44040</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44042</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44043</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44043</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44047</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44049</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44049</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44053</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44053</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44054</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44054</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44056</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44057</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44061</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44062</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44062</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44067</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44085</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>44085</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44085</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>44089</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44104</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44106</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>44109</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>44110</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44113</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44123</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44127</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44127</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44138</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44138</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44138</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>44138</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>44139</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>44140</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>44140</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44145</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44146</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44152</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44158</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44158</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44160</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>44172</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44178</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44187</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44188</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44193</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44203</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44208</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44208</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>44208</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>44209</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44214</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44214</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44217</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>44218</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>44223</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>44230</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44237</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44242</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>44242</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>44242</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44246</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44246</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44246</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44248</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>44250</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44250</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44252</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44252</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>44260</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44260</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44260</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44263</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>44263</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>44265</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>44270</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44281</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44281</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44285</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44292</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44292</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44292</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44293</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44296</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44297</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44297</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>44297</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>44301</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>44301</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44302</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>44302</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44302</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44307</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44309</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44323</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44323</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44323</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44328</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44344</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44350</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>44350</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44358</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44360</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44360</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44360</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44360</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44365</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44365</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44365</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44371</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44378</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44378</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44379</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44381</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44381</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>44384</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44384</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44386</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44391</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44398</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>44404</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>44411</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>44413</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>44414</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>44414</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44421</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>44421</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44423</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44423</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44425</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44425</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44425</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44425</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44425</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44431</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44432</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44433</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44433</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44435</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44439</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44440</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44448</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44448</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44448</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44448</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44449</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44449</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44449</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44450</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44452</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44452</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44453</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44453</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44454</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44454</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44455</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44458</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44458</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44459</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44459</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44463</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44463</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>44463</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44466</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44469</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>44469</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44472</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44473</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44473</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44484</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44487</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44490</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44495</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44495</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44495</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44501</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44508</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44508</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44511</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44517</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44518</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44518</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44522</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44522</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44524</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44531</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44535</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44536</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44544</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44553</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44566</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44566</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44571</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>44578</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44579</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44580</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44580</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44588</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44588</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44596</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44596</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44602</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>44604</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44610</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44610</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44616</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44624</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44624</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44624</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44624</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44636</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44636</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44636</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44636</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44637</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44637</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44640</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44643</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44643</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44643</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44648</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44667</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44671</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44671</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44676</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44680</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44697</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>44697</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44701</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>44704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44705</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44715</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>44715</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>44719</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>44720</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>44722</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>44722</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>44722</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44724</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44725</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44733</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44739</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44739</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44742</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44745</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44745</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44746</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44752</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44752</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>44752</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>44752</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>44753</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44761</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44769</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44769</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44769</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>44769</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>44769</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>44770</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44771</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44774</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44778</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44778</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44785</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44785</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44785</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44785</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44785</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>44791</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>44795</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44796</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44803</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44807</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44807</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44814</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44817</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>44818</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>44819</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44823</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44824</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>44826</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44830</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>44837</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44838</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>44838</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44838</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44838</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44839</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>44839</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>44846</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>44846</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>44848</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>44848</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>44848</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>44851</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44854</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44854</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44854</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>44855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44855</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>44859</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>44859</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>44859</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>44862</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44862</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>44864</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>44865</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>44868</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>44868</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>44869</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44872</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44872</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44873</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44879</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44881</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44886</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44887</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>44887</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>44887</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>44895</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>44895</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>44895</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>44896</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>44896</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44897</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44897</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>44897</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44897</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44899</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44899</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44900</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44900</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>44902</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>44904</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44907</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44907</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>44907</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>44908</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>44909</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>44909</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>44909</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44909</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44911</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>44911</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>44914</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>44917</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>44917</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>44931</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>44942</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>44943</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>44943</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44949</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>44953</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>44958</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44958</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44960</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>44966</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44970</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>44972</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44977</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44977</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44979</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44979</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44979</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44979</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>44980</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>44985</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44985</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44985</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44986</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44988</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>44991</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>44991</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>44998</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45001</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45001</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44050,7 +44050,7 @@
         <v>45001</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>45007</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45007</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>45008</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>45012</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>45013</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44407,7 +44407,7 @@
         <v>45014</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45014</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44531,7 +44531,7 @@
         <v>45014</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>45016</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45022</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>45022</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>45022</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45022</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45029</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45030</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45030</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45030</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45030</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45034</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45036</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45036</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45039</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45039</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45039</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45039</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45041</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45043</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>45048</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45053</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45056</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45056</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45056</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45056</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45056</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45056</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45057</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45065</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45066</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45068</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45068</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45070</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>45070</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45072</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45073</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45073</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45079</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45081</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45081</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45082</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45091</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47126,7 +47126,7 @@
         <v>45098</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>45098</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>45103</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45103</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>45104</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>45104</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45105</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>45105</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47679,7 +47679,7 @@
         <v>45105</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>45105</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47803,7 +47803,7 @@
         <v>45110</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45110</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47922,7 +47922,7 @@
         <v>45112</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45113</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45114</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45114</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45114</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45114</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45118</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45119</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45121</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45121</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>45121</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48559,7 +48559,7 @@
         <v>45140</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>45140</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45140</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45140</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45141</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45141</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45142</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>45147</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45147</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45147</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45148</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45148</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45148</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49367,7 +49367,7 @@
         <v>45149</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>45154</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>45155</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45156</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45156</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49667,7 +49667,7 @@
         <v>45159</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>45159</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>45160</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45160</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45160</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45160</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45161</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45161</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45161</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45161</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45162</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45163</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45163</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45163</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>45163</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45163</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45166</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45166</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45166</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45168</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45169</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45169</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45169</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45170</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45174</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45175</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45175</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51231,7 +51231,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45180</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51345,7 +51345,7 @@
         <v>45182</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45182</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45182</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>45182</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45182</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         <v>45183</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45183</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45187</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45187</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45189</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         <v>45189</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51997,7 +51997,7 @@
         <v>45189</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45189</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45191</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45191</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45191</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45192</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45193</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52401,7 +52401,7 @@
         <v>45193</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>45195</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52515,7 +52515,7 @@
         <v>45195</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45195</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>45196</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52696,7 +52696,7 @@
         <v>45196</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>45196</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52815,7 +52815,7 @@
         <v>45201</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>45202</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45202</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52996,7 +52996,7 @@
         <v>45205</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45205</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45205</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45209</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45209</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45209</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45209</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45209</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45209</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45211</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45211</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45211</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45211</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45211</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45211</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45212</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45212</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>45213</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>45213</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45214</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45214</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54295,7 +54295,7 @@
         <v>45215</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>45215</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>45216</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54471,7 +54471,7 @@
         <v>45217</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45218</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45222</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54761,7 +54761,7 @@
         <v>45222</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54818,7 +54818,7 @@
         <v>45222</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54875,7 +54875,7 @@
         <v>45224</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45225</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45225</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45225</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45225</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45225</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45225</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45226</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>45228</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45228</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45230</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45230</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45230</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45230</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45231</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45231</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45231</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45231</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56077,7 +56077,7 @@
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45237</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>45239</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56330,7 +56330,7 @@
         <v>45239</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45240</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45243</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45243</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56739,7 +56739,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45250</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57034,7 +57034,7 @@
         <v>45250</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57091,7 +57091,7 @@
         <v>45250</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         <v>45250</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>45250</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45250</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45250</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45250</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
         <v>45252</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45256</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45256</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45256</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45257</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45260</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45264</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45264</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45266</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45268</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45268</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45270</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45271</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45272</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45272</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45278</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45280</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45299</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45299</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45299</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45299</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58873,7 +58873,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>45303</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45303</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45306</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45309</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45311</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45311</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45311</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59344,7 +59344,7 @@
         <v>45313</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59401,7 +59401,7 @@
         <v>45314</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59458,7 +59458,7 @@
         <v>45315</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45315</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45315</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45320</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45321</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45321</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45321</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45322</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45322</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45323</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45323</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>45323</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60147,7 +60147,7 @@
         <v>45327</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60204,7 +60204,7 @@
         <v>45327</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60254,14 +60254,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 4657-2024</t>
+          <t>A 4724-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60274,7 +60274,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -60311,14 +60311,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 4724-2024</t>
+          <t>A 4657-2024</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60331,7 +60331,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -60375,7 +60375,7 @@
         <v>45328</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45330</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>45330</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>45331</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60606,14 +60606,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 6104-2024</t>
+          <t>A 6109-2024</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -60663,14 +60663,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 6109-2024</t>
+          <t>A 6104-2024</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60683,7 +60683,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -60727,7 +60727,7 @@
         <v>45341</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60777,14 +60777,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 6964-2024</t>
+          <t>A 6982-2024</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -60834,14 +60834,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 6982-2024</t>
+          <t>A 6964-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -60898,7 +60898,7 @@
         <v>45345</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60955,7 +60955,7 @@
         <v>45345</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61005,14 +61005,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 7378-2024</t>
+          <t>A 7381-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -61062,14 +61062,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 7381-2024</t>
+          <t>A 7378-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -61126,7 +61126,7 @@
         <v>45348</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>45348</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61233,14 +61233,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 7951-2024</t>
+          <t>A 7960-2024</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>4.1</v>
+        <v>10.4</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -61297,7 +61297,7 @@
         <v>45350</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61347,14 +61347,14 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 7960-2024</t>
+          <t>A 7951-2024</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>10.4</v>
+        <v>4.1</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43544</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44883</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>44363</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44378</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43776</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>44832</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45209</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>43493</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43606</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>43752</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>43838</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45156</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>43668</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44071</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44578</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45002</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45039</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45105</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45142</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>43643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>43703</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44411</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44495</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44624</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44714</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44865</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44986</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45140</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45156</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45225</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45323</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45350</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>43363</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>43558</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>43661</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>43691</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43703</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>43703</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>43747</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>43754</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>43776</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43858</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>43860</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>43943</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>43957</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44014</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44127</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>44397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>44474</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44484</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44503</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>44503</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44533</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>44553</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44608</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44624</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44624</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>44637</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44735</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44792</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44798</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>44854</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44865</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44911</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44956</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44957</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>44971</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44986</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45156</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45166</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45209</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45212</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>45219</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>45323</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>45337</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>45350</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43324</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43334</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43347</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43347</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43347</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43347</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43347</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43357</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43368</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>43368</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43370</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>43371</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43374</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43388</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>43388</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43395</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43397</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43404</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43410</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43412</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43423</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>43424</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43426</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43437</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43444</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43446</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43450</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43455</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43472</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>43483</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>43490</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>43494</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>43495</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>43497</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>43503</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43522</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43522</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43535</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D129" t="inlineStr">
   